--- a/leave_of_absence_forms/044_law_enforcement_stress_leave_of_absence_form--leave_of_absence_forms.xlsx
+++ b/leave_of_absence_forms/044_law_enforcement_stress_leave_of_absence_form--leave_of_absence_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Employee's Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Start Date of Leave</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>End Date of Leave</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>Reason for Leave</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>attachments</t>
+          <t>Attachments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,151 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>reviewers</t>
+          <t>Reviewers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>attachments</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>attachments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>reviewers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>reviewers</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -845,10 +707,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -873,7 +735,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_name_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -890,7 +752,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_name_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -967,108 +829,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>department_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>attachments_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>attachments_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>reviewers_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>reviewers_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
